--- a/4.evidence/ELC/全社リスクアセスメント結果_2025年度.xlsx
+++ b/4.evidence/ELC/全社リスクアセスメント結果_2025年度.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="全社リスク評価" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="不正リスク評価" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +44,17 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -95,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,6 +126,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -852,4 +870,874 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【ELC-005 統制実施記録】 2025年度 不正リスク評価シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>実施日: 2025/6/18 / 実施者: 内部監査室（長谷川 剛 IA001・大塚 美穂 IA002）・経理部（佐藤 一郎 ACC001・高橋 美咲 ACC002）合同 / 取締役会報告: 2025/6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>根拠: R03 内部監査規程 §4 / 統制記述: 決算期前に不正リスクファクター（動機・機会・正当化）を検討し、重要拠点・勘定について不正シナリオを評価する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>■ セクション1: 不正リスクファクター評価（Fraud Triangle）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>対象プロセス/勘定</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>動機（Pressure）</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>機会（Opportunity）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>正当化（Rationalization）</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>総合評価</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>評価根拠</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>リンク統制</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>FT-01</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>売上計上（PLC-S）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>中：半期業績コミットメントのプレッシャー</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>中：与信超過受注の個別承認が属人的</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>低：営業現場に「期ずれ調整」の慣習は限定的</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>ITAC-001自動統制に依存する構造のため個別承認ログをモニタリングで補完</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>PLC-S-001 / ITAC-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FT-02</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>購買発注（PLC-P）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>中：仕入先からのリベート誘因リスク</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>高：SAPロールでSoD違反ユーザが存在する可能性</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>中：「効率化のため一時的に権限を拡張」との正当化</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>PUR004に関する職務分掌違反の懸念を内部監査室が認識済。ITGC-AC-004の補完統制と合わせて重点監視</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>PLC-P-002 / ELC-007 / ITGC-AC-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FT-03</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>棚卸資産評価（PLC-I）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>低：原価変動の業績影響は限定的</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>中：倉庫課による差異分析と経理部の連携に依存</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>中：「軽微差異は調整仕訳で十分」との慣習</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>倉庫差異調整の原因分析・経理報告プロセスを重点テスト対象に設定</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>PLC-I-001 / PLC-I-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FT-04</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>会計上見積り（FCRP）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>中：四半期利益目標達成プレッシャー</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>中：貸倒・滞留評価は経理部課長の裁量余地あり</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>低：「保守的評価の範囲内」との正当化</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>見積前提の外部情報・内部情報の根拠資料を重点確認</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-003 / PLC-I-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>FT-05</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>連結仕訳</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>中：連結利益調整余地の存在</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>中：非定型連結仕訳のレビューが経理部長の単独判断</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>低：「実務慣行」として正当化される余地</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>連結パッケージのバリデーションで補完。非定型仕訳のレビュー記録を重点確認</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-004 / ITAC-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FT-06</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>経費精算・交際費</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>低：個人レベルの生活資金プレッシャー</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>中：承認者の確認が形式的になるリスク</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>低：「業界慣行」との正当化</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>金額閾値超過分のみ抽出レビュー</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>PLC-P-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>FT-07</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>固定資産計上・減損</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>低：減損回避の業績プレッシャー（現時点では低）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>中：見積の主観性（将来キャッシュフロー）</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>低：「保守的評価の過大解釈」</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>ITAC-003自動計算に依存。減損兆候判定の前提を重点確認</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-003 / ITAC-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>FT-08</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>海外子会社取引（タイTPT）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>中：現地目標達成プレッシャー</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>中：親会社モニタリング頻度の低さ</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>中：「現地商慣習」としての正当化</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-002連結パッケージ検証で補完。現地内部監査を年1回実施</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-002 / ELC-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>■ セクション2: 重要拠点・勘定別 不正シナリオ評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>シナリオ№</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>重要拠点</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>重要勘定</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>不正シナリオ</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>発生可能性</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>影響度</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>対応策</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>売上高・売掛金</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>期末前倒し出荷による売上架空計上（カットオフ違反）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>PLC-S-006 期末カットオフ統制で全数検証 / 監査人サンプル実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>買掛金・仕入</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>架空仕入先への発注・送金（仕入先マスタ不正登録）</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>PLC-P-005 仕入先マスタ管理 + 反社チェック強化</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>本社倉庫A/B</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>棚卸資産</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>実地棚卸帳簿操作による在庫水増し</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>PLC-I-001 経理部立会 + 抽取検査 / 監査人立会予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>タイ TPT</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>売上高・売掛金</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>現地取引先への値引きを用いた裏金化</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>海外子会社内部監査（年1回）+ 連結パッケージ検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>接待交際費の私的流用・架空計上</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>金額閾値超過分のサンプルレビュー / 内部通報窓口周知</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>連結利益</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>非定型連結仕訳による利益操作</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-004 連結仕訳承認で2段階レビュー徹底</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>F-007</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>本社</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>貸倒引当金</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>回収不能債権の引当過少設定による利益操作</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>FCRP-003 + 監査法人連携で前提確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>東北子会社</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>製造原価</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>仕掛品評価の恣意的操作</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>PLC-I-007 月次締め + 連結パッケージ検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>■ セクション3: 総合評価と対応方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>1. 最重点領域: 購買発注プロセス（FT-02）。SoD違反（PUR004）の是正状況をITGC-AC-004・PLC-P-002と連携して継続監視する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2. 重点領域: 売上カットオフ（F-001）、棚卸在庫（FT-03/F-003）、会計上見積り（FT-04/F-007）、連結仕訳（FT-05/F-006）、海外子会社取引（FT-08/F-004）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>3. 共通: 内部通報窓口の周知を四半期に1回実施し、正当化を抑制する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>4. 監査計画への反映: 本評価結果を内部監査年次計画（ELC-010）および外部監査人との協議に反映済み（2025/6/25協議）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>承認: 内部監査室長 [印] 長谷川 剛 2025/6/20 / 経理部長 [印] 佐藤 一郎 2025/6/20 / 取締役会審議: 2025/6/30（第242回）/ 監査等委員会報告: 2025/6/27</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/4.evidence/ELC/全社リスクアセスメント結果_2025年度.xlsx
+++ b/4.evidence/ELC/全社リスクアセスメント結果_2025年度.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全社リスク評価" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FinancialReportingRisks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FraudRisk" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeTriggers" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +30,7 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <i val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -41,12 +38,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -56,16 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,40 +62,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00888888"/>
+        <color rgb="00B7B7B7"/>
       </left>
       <right style="thin">
-        <color rgb="00888888"/>
+        <color rgb="00B7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="00888888"/>
+        <color rgb="00B7B7B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00888888"/>
+        <color rgb="00B7B7B7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,377 +451,852 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【ELC-004 統制実施記録】 2025年度 全社リスクアセスメント結果</t>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>実施日: 2025/6/15 / 実施者: 経営企画部 / 取締役会報告: 2025/6/30</t>
+          <t>評価名</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 財務報告に係る全社リスクアセスメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>リスク№</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>リスク記述</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>経営企画部、内部監査室、経理部、情報システム部</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>承認/報告</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-30 取締役会報告、J-SOX評価範囲承認</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>親会社及び連結子会社4社、重要な業務プロセス、決算・財務報告プロセス、財務報告関連IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>結論</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>売上、在庫、購買、決算、ITアクセス/変更、外部委託をFY2025の重点評価領域とする。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>リスクID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>領域</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>財務報告リスク</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>影響勘定/開示</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>関連アサーション</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>発生可能性</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>影響度</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>対応策</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>対応統制/評価範囲</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>責任部門</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>販売</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>出荷基準の不適切適用又は押込み出荷</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>売上高、売掛金</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>実在性、期間帰属</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>PLC-S-001/002/006、FCRP-005</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>営業本部/経理部</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>購買</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>架空発注又は承認権限逸脱による不正支出</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>仕入高、買掛金、原材料</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>実在性、権利義務</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>PLC-P-002/004、ITAC-004</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>購買部/経理部</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>在庫</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>実地棚卸差異及び滞留在庫評価の見落とし</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>棚卸資産、売上原価</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>実在性、評価</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>PLC-I-001/002/005</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>製造本部/経理部</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>R-001</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>事業環境</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>半導体市況の急落による販売減少</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>決算</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>会計上の見積りの根拠不足又は恣意的判断</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>貸倒引当金、減損、税効果</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>評価、表示</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>多角化戦略の継続、自動車分野強化</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>FCRP-003、ELC-005/009</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>経理部</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>R-002</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>サプライチェーン</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>特殊合金の調達難・価格高騰</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>不適切なアクセス権又は変更により財務データが改竄される</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>全勘定</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>全般</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>複数調達先の確保、長期契約</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC、ITGC-CM、ELC-012</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>情報システム部</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>R-003</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>為替</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>円安による輸入原材料コスト増</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>連結/開示</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>子会社パッケージ誤り、連結消去漏れ、開示遅延</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>連結財務諸表、注記</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>網羅性、表示</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>FCRP-002/005、ELC-007/009</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>経理部/経営企画部</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>不正リスクID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>シナリオ</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>動機/機会/正当化</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>影響</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>対応統制</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>残余リスク</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>監査計画への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>F-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>売上前倒し又は押込み出荷</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>業績目標未達の圧力、期末出荷判断の裁量</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>売上高過大</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>PLC-S-002/006、FCRP-005、ELC-009</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>期末カットオフと請求/出荷突合を重点化</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>F-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>発注承認権限逸脱又はキックバック</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>購買担当者と仕入先の癒着機会</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>仕入高/買掛金過大、資産流出</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>PLC-P-002/004、内部通報ELC-008</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>為替ヘッジの検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>R-004</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>人材</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>熟練工の高齢化・後継者不足</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>発注承認例外3件を不備台帳でフォロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>F-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>棚卸差異・評価損の隠蔽</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>評価損計上回避の動機、Excel見積りの裁量</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>棚卸資産過大</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PLC-I-002/005、FCRP-003</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>棚卸差異と評価損計算の追加検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>F-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>手入力仕訳による見積り調整</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>経営者による統制無視の機会</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>期間損益操作</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>FCRP-001/004、ELC-001/011</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>教育訓練プログラム強化、自動化推進</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>R-005</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>IT/セキュリティ</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>サイバー攻撃による業務停止</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>セキュリティ投資継続、演習実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>R-006</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>コンプライアンス</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>輸出規制違反（米中対立）</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>輸出管理体制の強化、専門部署化</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>R-007</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>財務報告</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>会計上見積りの不適切な設定</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>3段階レビュー、外部監査連携</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>R-008</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>環境</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>カーボンニュートラル規制対応遅延</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>CO2削減計画の策定・実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>承認: 経営企画部長 [印] 2025/6/20 / 取締役会審議: 2025/6/30</t>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>非定型仕訳と承認ログを重点確認</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>発生日</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>変化事象</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>財務報告への影響</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>再評価結果</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>職務権限規程R18改訂</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>承認権限とSAPロール設計に影響</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>評価範囲変更なし</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ELC-003/006でレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>リスク管理規程R05改訂</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>全社リスク評価プロセスを更新</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>評価プロセス更新</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>取締役会承認済</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>タイ子会社の受注増加</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>連結パッケージ及び在庫評価への影響</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>子会社パッケージ確認を強化</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FCRP-002/ELC-009へ反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>退職者アカウント停止遅延</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>財務データ改竄リスク</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ITGC不備として評価</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ITGC-AC-003/ELC-011で是正管理</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>